--- a/files/九龙-启德-Monaco One.xlsx
+++ b/files/九龙-启德-Monaco One.xlsx
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>10381000</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>23381</v>
+        <v>23328</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>10381000</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>23381</v>
+        <v>23328</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -32555,9 +32555,9 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>F | 444呎 (2房)
+          <t>F | 445呎 (2房)
 $1038万
-$23,381/呎
+$23,328/呎
 (21年-12月-08日)</t>
         </is>
       </c>
